--- a/research/traditional_assets/database/data/ghana/ghana_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1415</v>
+        <v>0.187</v>
       </c>
       <c r="E2">
-        <v>0.136</v>
-      </c>
-      <c r="F2">
-        <v>0.15</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>361</v>
+        <v>158.8</v>
       </c>
       <c r="L2">
-        <v>0.3487248840803709</v>
+        <v>0.2774768478070942</v>
       </c>
       <c r="M2">
-        <v>97.9042</v>
+        <v>47.554</v>
       </c>
       <c r="N2">
-        <v>0.07820448917645179</v>
+        <v>0.0914148404459823</v>
       </c>
       <c r="O2">
-        <v>0.2712027700831025</v>
+        <v>0.2994584382871537</v>
       </c>
       <c r="P2">
-        <v>97.8082</v>
+        <v>47.554</v>
       </c>
       <c r="Q2">
-        <v>0.07812780573528237</v>
+        <v>0.0914148404459823</v>
       </c>
       <c r="R2">
-        <v>0.2709368421052631</v>
+        <v>0.2994584382871537</v>
       </c>
       <c r="S2">
-        <v>0.09600000000000009</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0009805503747540973</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1710.2</v>
+        <v>1152.6</v>
       </c>
       <c r="V2">
-        <v>1.366083552999441</v>
+        <v>2.215686274509804</v>
       </c>
       <c r="W2">
-        <v>0.2452616690240453</v>
+        <v>0.1020124764533799</v>
       </c>
       <c r="X2">
-        <v>0.09510983079673334</v>
+        <v>0.2553754349334268</v>
       </c>
       <c r="Y2">
-        <v>0.1501518382273119</v>
+        <v>-0.1533629584800469</v>
       </c>
       <c r="Z2">
-        <v>4.21498371335505</v>
+        <v>0.8352305896088732</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08485424933651611</v>
+        <v>0.1992194945802304</v>
       </c>
       <c r="AC2">
-        <v>-0.08485424933651611</v>
+        <v>-0.1992194945802304</v>
       </c>
       <c r="AD2">
-        <v>479.1</v>
+        <v>734.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>479.1</v>
+        <v>734.99</v>
       </c>
       <c r="AG2">
-        <v>-1231.1</v>
+        <v>-417.6099999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2767764298093588</v>
+        <v>0.5855607517586978</v>
       </c>
       <c r="AI2">
-        <v>0.2359401162218064</v>
+        <v>0.4619121537968439</v>
       </c>
       <c r="AJ2">
-        <v>-59.18749999999948</v>
+        <v>-4.070669655911876</v>
       </c>
       <c r="AK2">
-        <v>-3.84238451935081</v>
+        <v>-0.9521648920404017</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ecobank Ghana Limited (GHSE:EGH)</t>
+          <t>Republic Bank (Ghana) PLC (GHSE:RBGH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +710,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.138</v>
-      </c>
-      <c r="E3">
-        <v>0.153</v>
+        <v>0.166</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +725,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>105.4</v>
+        <v>9.34</v>
       </c>
       <c r="L3">
-        <v>0.3368488334931288</v>
+        <v>0.205726872246696</v>
       </c>
       <c r="M3">
-        <v>29.7</v>
+        <v>1.704</v>
       </c>
       <c r="N3">
-        <v>0.0745669093648004</v>
+        <v>0.03610169491525424</v>
       </c>
       <c r="O3">
-        <v>0.2817836812144212</v>
+        <v>0.182441113490364</v>
       </c>
       <c r="P3">
-        <v>29.7</v>
+        <v>1.704</v>
       </c>
       <c r="Q3">
-        <v>0.0745669093648004</v>
+        <v>0.03610169491525424</v>
       </c>
       <c r="R3">
-        <v>0.2817836812144212</v>
+        <v>0.182441113490364</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>482.4</v>
+        <v>85.3</v>
       </c>
       <c r="V3">
-        <v>1.211147376349485</v>
+        <v>1.807203389830508</v>
       </c>
       <c r="W3">
-        <v>0.2909994478188846</v>
+        <v>0.08010291595197255</v>
       </c>
       <c r="X3">
-        <v>0.0792041334553832</v>
+        <v>0.1746283586001935</v>
       </c>
       <c r="Y3">
-        <v>0.2117953143635014</v>
+        <v>-0.09452544264822091</v>
       </c>
       <c r="Z3">
-        <v>-6.438271604938268</v>
+        <v>4.053571428571432</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07847778658301575</v>
+        <v>0.1697682049386209</v>
       </c>
       <c r="AC3">
-        <v>-0.07847778658301575</v>
+        <v>-0.1697682049386209</v>
       </c>
       <c r="AD3">
-        <v>21.1</v>
+        <v>9.49</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.1</v>
+        <v>9.49</v>
       </c>
       <c r="AG3">
-        <v>-461.3</v>
+        <v>-75.81</v>
       </c>
       <c r="AH3">
-        <v>0.0503099666189795</v>
+        <v>0.1674016581407655</v>
       </c>
       <c r="AI3">
-        <v>0.04521105635311763</v>
+        <v>0.108098872308919</v>
       </c>
       <c r="AJ3">
-        <v>7.322222222222228</v>
+        <v>2.64977280671094</v>
       </c>
       <c r="AK3">
-        <v>29.38216560509566</v>
+        <v>-30.44578313253018</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Ghana PLC (GHSE:SCB)</t>
+          <t>Agricultural Development Bank Plc (GHSE:ADB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +829,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.24</v>
-      </c>
-      <c r="E4">
-        <v>0.387</v>
+        <v>0.173</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,85 +844,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>87</v>
+        <v>3.26</v>
       </c>
       <c r="L4">
-        <v>0.4904171364148816</v>
+        <v>0.05488215488215488</v>
       </c>
       <c r="M4">
-        <v>38.9</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0875140607424072</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4471264367816092</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>38.9</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0875140607424072</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4471264367816092</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>489.7</v>
+        <v>152.2</v>
       </c>
       <c r="V4">
-        <v>1.101687289088864</v>
+        <v>0.8455555555555555</v>
       </c>
       <c r="W4">
-        <v>0.3730703259005146</v>
+        <v>0.02071156289707751</v>
       </c>
       <c r="X4">
-        <v>0.08039553051158604</v>
+        <v>0.1965668651231237</v>
       </c>
       <c r="Y4">
-        <v>0.2926747953889285</v>
+        <v>-0.1758553022260462</v>
       </c>
       <c r="Z4">
-        <v>-0.5752269779507134</v>
+        <v>0.4644253322908522</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07925473985134186</v>
+        <v>0.1834472765068557</v>
       </c>
       <c r="AC4">
-        <v>-0.07925473985134186</v>
+        <v>-0.1834472765068557</v>
       </c>
       <c r="AD4">
-        <v>35</v>
+        <v>80.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>35</v>
+        <v>80.8</v>
       </c>
       <c r="AG4">
-        <v>-454.7</v>
+        <v>-71.39999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.072992700729927</v>
+        <v>0.3098159509202454</v>
       </c>
       <c r="AI4">
-        <v>0.1137841352405722</v>
+        <v>0.4572722127900397</v>
       </c>
       <c r="AJ4">
-        <v>44.57843137254907</v>
+        <v>-0.6574585635359115</v>
       </c>
       <c r="AK4">
-        <v>2.496979681493685</v>
+        <v>-2.914285714285712</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GCB Bank Limited (GHSE:GCB)</t>
+          <t>GCB Bank Plc (GHSE:GCB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,13 +945,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.141</v>
+        <v>0.201</v>
       </c>
       <c r="E5">
-        <v>0.0663</v>
-      </c>
-      <c r="F5">
-        <v>0.15</v>
+        <v>0.329</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>86.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L5">
-        <v>0.2629663330300273</v>
+        <v>0.2726897689768977</v>
       </c>
       <c r="M5">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="N5">
-        <v>0.04836601307189543</v>
+        <v>0.1213818860877685</v>
       </c>
       <c r="O5">
-        <v>0.1280276816608996</v>
+        <v>0.1966717095310136</v>
       </c>
       <c r="P5">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="Q5">
-        <v>0.04836601307189543</v>
+        <v>0.1213818860877685</v>
       </c>
       <c r="R5">
-        <v>0.1280276816608996</v>
+        <v>0.1966717095310136</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +993,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>368.5</v>
+        <v>407.8</v>
       </c>
       <c r="V5">
-        <v>1.605664488017429</v>
+        <v>3.80765639589169</v>
       </c>
       <c r="W5">
-        <v>0.2452616690240453</v>
+        <v>0.1592387376535774</v>
       </c>
       <c r="X5">
-        <v>0.09510983079673334</v>
+        <v>0.2269207616569027</v>
       </c>
       <c r="Y5">
-        <v>0.1501518382273119</v>
+        <v>-0.06768202400332526</v>
       </c>
       <c r="Z5">
-        <v>12.82879377431907</v>
+        <v>1.760348583877995</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08485424933651611</v>
+        <v>0.1909833738666697</v>
       </c>
       <c r="AC5">
-        <v>-0.08485424933651611</v>
+        <v>-0.1909833738666697</v>
       </c>
       <c r="AD5">
-        <v>91.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>91.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="AG5">
-        <v>-277.4</v>
+        <v>-323</v>
       </c>
       <c r="AH5">
-        <v>0.284154709918902</v>
+        <v>0.4418968212610735</v>
       </c>
       <c r="AI5">
-        <v>0.1799683919399447</v>
+        <v>0.2223387519664394</v>
       </c>
       <c r="AJ5">
-        <v>5.791231732776621</v>
+        <v>1.496062992125984</v>
       </c>
       <c r="AK5">
-        <v>-2.014524328249818</v>
+        <v>12.2348484848485</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1058,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Access Bank (Ghana) Plc (GHSE:ACCESS)</t>
+          <t>Societe Generale Ghana PLC (GHSE:SOGEGH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,6 +1066,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.137</v>
+      </c>
+      <c r="E6">
+        <v>0.4379999999999999</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1094,28 +1085,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>41.2</v>
+        <v>18.7</v>
       </c>
       <c r="L6">
-        <v>0.4095427435387675</v>
+        <v>0.2903726708074534</v>
       </c>
       <c r="M6">
-        <v>6.6082</v>
+        <v>12.6</v>
       </c>
       <c r="N6">
-        <v>0.07367001114827201</v>
+        <v>0.1733149931224209</v>
       </c>
       <c r="O6">
-        <v>0.1603932038834952</v>
+        <v>0.6737967914438503</v>
       </c>
       <c r="P6">
-        <v>6.6082</v>
+        <v>12.6</v>
       </c>
       <c r="Q6">
-        <v>0.07367001114827201</v>
+        <v>0.1733149931224209</v>
       </c>
       <c r="R6">
-        <v>0.1603932038834952</v>
+        <v>0.6737967914438503</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1115,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>201.7</v>
+        <v>162.8</v>
       </c>
       <c r="V6">
-        <v>2.24860646599777</v>
+        <v>2.239339752407153</v>
       </c>
       <c r="W6">
-        <v>0.2332955832389581</v>
+        <v>0.1047032474804031</v>
       </c>
       <c r="X6">
-        <v>0.1136647443208798</v>
+        <v>0.2838301082099509</v>
       </c>
       <c r="Y6">
-        <v>0.1196308389180783</v>
+        <v>-0.1791268607295477</v>
       </c>
       <c r="Z6">
-        <v>1.100656455142232</v>
+        <v>2.308243727598569</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08940754550916752</v>
+        <v>0.2074556152937912</v>
       </c>
       <c r="AC6">
-        <v>-0.08940754550916752</v>
+        <v>-0.2074556152937912</v>
       </c>
       <c r="AD6">
-        <v>71.59999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>71.59999999999999</v>
+        <v>104.3</v>
       </c>
       <c r="AG6">
-        <v>-130.1</v>
+        <v>-58.50000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.4438933663980161</v>
+        <v>0.5892655367231638</v>
       </c>
       <c r="AI6">
-        <v>0.2526464361326747</v>
+        <v>0.486473880597015</v>
       </c>
       <c r="AJ6">
-        <v>3.220297029702971</v>
+        <v>-4.119718309859159</v>
       </c>
       <c r="AK6">
-        <v>-1.592411260709914</v>
+        <v>-1.133720930232559</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,117 +1180,239 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Access Bank (Ghana) Plc (GHSE:ACCESS)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.397</v>
+      </c>
+      <c r="E7">
+        <v>0.514</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>40.9</v>
+      </c>
+      <c r="L7">
+        <v>0.458006718924972</v>
+      </c>
+      <c r="M7">
+        <v>13.5</v>
+      </c>
+      <c r="N7">
+        <v>0.1888111888111888</v>
+      </c>
+      <c r="O7">
+        <v>0.3300733496332519</v>
+      </c>
+      <c r="P7">
+        <v>13.5</v>
+      </c>
+      <c r="Q7">
+        <v>0.1888111888111888</v>
+      </c>
+      <c r="R7">
+        <v>0.3300733496332519</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>216.6</v>
+      </c>
+      <c r="V7">
+        <v>3.02937062937063</v>
+      </c>
+      <c r="W7">
+        <v>0.1931067044381492</v>
+      </c>
+      <c r="X7">
+        <v>0.3774555190346738</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1843488145965246</v>
+      </c>
+      <c r="Z7">
+        <v>1.093023255813954</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.2181424004712712</v>
+      </c>
+      <c r="AC7">
+        <v>-0.2181424004712712</v>
+      </c>
+      <c r="AD7">
+        <v>178.2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>178.2</v>
+      </c>
+      <c r="AG7">
+        <v>-38.40000000000001</v>
+      </c>
+      <c r="AH7">
+        <v>0.7136563876651982</v>
+      </c>
+      <c r="AI7">
+        <v>0.5586206896551724</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.16012084592145</v>
+      </c>
+      <c r="AK7">
+        <v>-0.3750000000000001</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>CalBank PLC (GHSE:CAL)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.142</v>
-      </c>
-      <c r="E7">
-        <v>0.119</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>40.7</v>
-      </c>
-      <c r="L7">
-        <v>0.3551483420593369</v>
-      </c>
-      <c r="M7">
-        <v>11.596</v>
-      </c>
-      <c r="N7">
-        <v>0.1289877641824249</v>
-      </c>
-      <c r="O7">
-        <v>0.2849140049140049</v>
-      </c>
-      <c r="P7">
-        <v>11.5</v>
-      </c>
-      <c r="Q7">
-        <v>0.1279199110122358</v>
-      </c>
-      <c r="R7">
-        <v>0.2825552825552826</v>
-      </c>
-      <c r="S7">
-        <v>0.09600000000000009</v>
-      </c>
-      <c r="T7">
-        <v>0.008278716798896179</v>
-      </c>
-      <c r="U7">
-        <v>167.9</v>
-      </c>
-      <c r="V7">
-        <v>1.867630700778643</v>
-      </c>
-      <c r="W7">
-        <v>0.2203573362208988</v>
-      </c>
-      <c r="X7">
-        <v>0.2106422004138203</v>
-      </c>
-      <c r="Y7">
-        <v>0.009715135807078501</v>
-      </c>
-      <c r="Z7">
-        <v>0.2360453141091658</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.09794173204621767</v>
-      </c>
-      <c r="AC7">
-        <v>-0.09794173204621767</v>
-      </c>
-      <c r="AD7">
-        <v>260.3</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>260.3</v>
-      </c>
-      <c r="AG7">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.7432895488292404</v>
-      </c>
-      <c r="AI7">
-        <v>0.5577458752946218</v>
-      </c>
-      <c r="AJ7">
-        <v>0.5068568294020844</v>
-      </c>
-      <c r="AK7">
-        <v>0.3092369477911647</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="D8">
+        <v>0.298</v>
+      </c>
+      <c r="E8">
+        <v>0.448</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>20.5</v>
+      </c>
+      <c r="L8">
+        <v>0.2871148459383753</v>
+      </c>
+      <c r="M8">
+        <v>6.75</v>
+      </c>
+      <c r="N8">
+        <v>0.1618705035971223</v>
+      </c>
+      <c r="O8">
+        <v>0.3292682926829268</v>
+      </c>
+      <c r="P8">
+        <v>6.75</v>
+      </c>
+      <c r="Q8">
+        <v>0.1618705035971223</v>
+      </c>
+      <c r="R8">
+        <v>0.3292682926829268</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>127.9</v>
+      </c>
+      <c r="V8">
+        <v>3.067146282973621</v>
+      </c>
+      <c r="W8">
+        <v>0.09932170542635659</v>
+      </c>
+      <c r="X8">
+        <v>0.7457067361183396</v>
+      </c>
+      <c r="Y8">
+        <v>-0.6463850306919831</v>
+      </c>
+      <c r="Z8">
+        <v>0.2389558232931727</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.2315159176591471</v>
+      </c>
+      <c r="AC8">
+        <v>-0.2315159176591471</v>
+      </c>
+      <c r="AD8">
+        <v>277.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>277.4</v>
+      </c>
+      <c r="AG8">
+        <v>149.5</v>
+      </c>
+      <c r="AH8">
+        <v>0.8693199623942338</v>
+      </c>
+      <c r="AI8">
+        <v>0.6734644331148337</v>
+      </c>
+      <c r="AJ8">
+        <v>0.7819037656903765</v>
+      </c>
+      <c r="AK8">
+        <v>0.5264084507042253</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/ghana/ghana_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.187</v>
+        <v>0.0809</v>
       </c>
       <c r="E2">
-        <v>0.4429999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>158.8</v>
+        <v>-110.73</v>
       </c>
       <c r="L2">
-        <v>0.2774768478070942</v>
+        <v>-0.3756105834464044</v>
       </c>
       <c r="M2">
-        <v>47.554</v>
+        <v>0.012</v>
       </c>
       <c r="N2">
-        <v>0.0914148404459823</v>
+        <v>2.416918429003021e-05</v>
       </c>
       <c r="O2">
-        <v>0.2994584382871537</v>
+        <v>-0.0001083717149823896</v>
       </c>
       <c r="P2">
-        <v>47.554</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0914148404459823</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.2994584382871537</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>1152.6</v>
+        <v>1486.5</v>
       </c>
       <c r="V2">
-        <v>2.215686274509804</v>
+        <v>2.993957703927492</v>
       </c>
       <c r="W2">
-        <v>0.1020124764533799</v>
+        <v>-0.08340047653958944</v>
       </c>
       <c r="X2">
-        <v>0.2553754349334268</v>
+        <v>0.153935020395158</v>
       </c>
       <c r="Y2">
-        <v>-0.1533629584800469</v>
+        <v>-0.2373354969347474</v>
       </c>
       <c r="Z2">
-        <v>0.8352305896088732</v>
+        <v>0.5573305605444748</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1992194945802304</v>
+        <v>0.1390196541636267</v>
       </c>
       <c r="AC2">
-        <v>-0.1992194945802304</v>
+        <v>-0.1390196541636267</v>
       </c>
       <c r="AD2">
-        <v>734.99</v>
+        <v>375.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>734.99</v>
+        <v>375.9</v>
       </c>
       <c r="AG2">
-        <v>-417.6099999999999</v>
+        <v>-1110.6</v>
       </c>
       <c r="AH2">
-        <v>0.5855607517586978</v>
+        <v>0.4308803301237964</v>
       </c>
       <c r="AI2">
-        <v>0.4619121537968439</v>
+        <v>0.339873417721519</v>
       </c>
       <c r="AJ2">
-        <v>-4.070669655911876</v>
+        <v>1.808500244259893</v>
       </c>
       <c r="AK2">
-        <v>-0.9521648920404017</v>
+        <v>2.918791064388963</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.166</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>9.34</v>
+        <v>-3.79</v>
       </c>
       <c r="L3">
-        <v>0.205726872246696</v>
+        <v>-0.09643765903307888</v>
       </c>
       <c r="M3">
-        <v>1.704</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03610169491525424</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.182441113490364</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.704</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03610169491525424</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.182441113490364</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>85.3</v>
+        <v>184.3</v>
       </c>
       <c r="V3">
-        <v>1.807203389830508</v>
+        <v>5.388888888888888</v>
       </c>
       <c r="W3">
-        <v>0.08010291595197255</v>
+        <v>-0.04890322580645162</v>
       </c>
       <c r="X3">
-        <v>0.1746283586001935</v>
+        <v>0.1144889409373599</v>
       </c>
       <c r="Y3">
-        <v>-0.09452544264822091</v>
+        <v>-0.1633921667438115</v>
       </c>
       <c r="Z3">
-        <v>4.053571428571432</v>
+        <v>23.25443786982251</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1697682049386209</v>
+        <v>0.1144889409373599</v>
       </c>
       <c r="AC3">
-        <v>-0.1697682049386209</v>
+        <v>-0.1144889409373599</v>
       </c>
       <c r="AD3">
-        <v>9.49</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.49</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-75.81</v>
+        <v>-184.3</v>
       </c>
       <c r="AH3">
-        <v>0.1674016581407655</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.108098872308919</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2.64977280671094</v>
+        <v>1.227848101265823</v>
       </c>
       <c r="AK3">
-        <v>-30.44578313253018</v>
+        <v>1.595670995670996</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agricultural Development Bank Plc (GHSE:ADB)</t>
+          <t>Ecobank Ghana PLC (GHSE:EGH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,7 +826,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.173</v>
+        <v>0.0809</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.26</v>
+        <v>-6.94</v>
       </c>
       <c r="L4">
-        <v>0.05488215488215488</v>
+        <v>-0.05039941902687001</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,7 +853,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -865,61 +862,61 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>152.2</v>
+        <v>564.5</v>
       </c>
       <c r="V4">
-        <v>0.8455555555555555</v>
+        <v>3.798788694481831</v>
       </c>
       <c r="W4">
-        <v>0.02071156289707751</v>
+        <v>-0.0260119940029985</v>
       </c>
       <c r="X4">
-        <v>0.1965668651231237</v>
+        <v>0.1207157060985929</v>
       </c>
       <c r="Y4">
-        <v>-0.1758553022260462</v>
+        <v>-0.1467277001015914</v>
       </c>
       <c r="Z4">
-        <v>0.4644253322908522</v>
+        <v>2.126312538604076</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1834472765068557</v>
+        <v>0.1208295596232272</v>
       </c>
       <c r="AC4">
-        <v>-0.1834472765068557</v>
+        <v>-0.1208295596232272</v>
       </c>
       <c r="AD4">
-        <v>80.8</v>
+        <v>16.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>80.8</v>
+        <v>16.3</v>
       </c>
       <c r="AG4">
-        <v>-71.39999999999999</v>
+        <v>-548.2</v>
       </c>
       <c r="AH4">
-        <v>0.3098159509202454</v>
+        <v>0.09884778653729533</v>
       </c>
       <c r="AI4">
-        <v>0.4572722127900397</v>
+        <v>0.05182829888712242</v>
       </c>
       <c r="AJ4">
-        <v>-0.6574585635359115</v>
+        <v>1.371871871871872</v>
       </c>
       <c r="AK4">
-        <v>-2.914285714285712</v>
+        <v>2.1928</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GCB Bank Plc (GHSE:GCB)</t>
+          <t>Agricultural Development Bank Plc (GHSE:ADB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,10 +942,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.201</v>
-      </c>
-      <c r="E5">
-        <v>0.329</v>
+        <v>-0.0213</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -963,85 +957,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>66.09999999999999</v>
+        <v>-35.5</v>
       </c>
       <c r="L5">
-        <v>0.2726897689768977</v>
+        <v>-1.25886524822695</v>
       </c>
       <c r="M5">
-        <v>13</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1213818860877685</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1966717095310136</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>13</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1213818860877685</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1966717095310136</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>407.8</v>
+        <v>207.4</v>
       </c>
       <c r="V5">
-        <v>3.80765639589169</v>
+        <v>1.415699658703072</v>
       </c>
       <c r="W5">
-        <v>0.1592387376535774</v>
+        <v>-0.370177267987487</v>
       </c>
       <c r="X5">
-        <v>0.2269207616569027</v>
+        <v>0.1366143941499362</v>
       </c>
       <c r="Y5">
-        <v>-0.06768202400332526</v>
+        <v>-0.5067916621374232</v>
       </c>
       <c r="Z5">
-        <v>1.760348583877995</v>
+        <v>1.151020408163265</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1909833738666697</v>
+        <v>0.1324786036997241</v>
       </c>
       <c r="AC5">
-        <v>-0.1909833738666697</v>
+        <v>-0.1324786036997241</v>
       </c>
       <c r="AD5">
-        <v>84.8</v>
+        <v>57.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>84.8</v>
+        <v>57.1</v>
       </c>
       <c r="AG5">
-        <v>-323</v>
+        <v>-150.3</v>
       </c>
       <c r="AH5">
-        <v>0.4418968212610735</v>
+        <v>0.2804518664047151</v>
       </c>
       <c r="AI5">
-        <v>0.2223387519664394</v>
+        <v>0.5</v>
       </c>
       <c r="AJ5">
-        <v>1.496062992125984</v>
+        <v>39.55263157894726</v>
       </c>
       <c r="AK5">
-        <v>12.2348484848485</v>
+        <v>1.612660944206008</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,10 +1058,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.137</v>
+        <v>0.194</v>
       </c>
       <c r="E6">
-        <v>0.4379999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1085,85 +1076,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>18.7</v>
+        <v>20.3</v>
       </c>
       <c r="L6">
-        <v>0.2903726708074534</v>
+        <v>0.2839160839160839</v>
       </c>
       <c r="M6">
-        <v>12.6</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.1733149931224209</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.6737967914438503</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>12.6</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.1733149931224209</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.6737967914438503</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>162.8</v>
+        <v>122.5</v>
       </c>
       <c r="V6">
-        <v>2.239339752407153</v>
+        <v>1.320043103448276</v>
       </c>
       <c r="W6">
-        <v>0.1047032474804031</v>
+        <v>0.184377838328792</v>
       </c>
       <c r="X6">
-        <v>0.2838301082099509</v>
+        <v>0.1712556466403798</v>
       </c>
       <c r="Y6">
-        <v>-0.1791268607295477</v>
+        <v>0.01312219168841225</v>
       </c>
       <c r="Z6">
-        <v>2.308243727598569</v>
+        <v>1.385658914728683</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.2074556152937912</v>
+        <v>0.1455607046275293</v>
       </c>
       <c r="AC6">
-        <v>-0.2074556152937912</v>
+        <v>-0.1455607046275293</v>
       </c>
       <c r="AD6">
-        <v>104.3</v>
+        <v>92.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>104.3</v>
+        <v>92.8</v>
       </c>
       <c r="AG6">
-        <v>-58.50000000000001</v>
+        <v>-29.7</v>
       </c>
       <c r="AH6">
-        <v>0.5892655367231638</v>
+        <v>0.5</v>
       </c>
       <c r="AI6">
-        <v>0.486473880597015</v>
+        <v>0.44106463878327</v>
       </c>
       <c r="AJ6">
-        <v>-4.119718309859159</v>
+        <v>-0.4706814580031697</v>
       </c>
       <c r="AK6">
-        <v>-1.133720930232559</v>
+        <v>-0.3378839590443687</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,10 +1177,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.397</v>
-      </c>
-      <c r="E7">
-        <v>0.514</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1207,85 +1192,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>40.9</v>
+        <v>-16.6</v>
       </c>
       <c r="L7">
-        <v>0.458006718924972</v>
+        <v>-0.9171270718232044</v>
       </c>
       <c r="M7">
-        <v>13.5</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.1888111888111888</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.3300733496332519</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>13.5</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1888111888111888</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.3300733496332519</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>216.6</v>
+        <v>217.5</v>
       </c>
       <c r="V7">
-        <v>3.02937062937063</v>
+        <v>4.420731707317073</v>
       </c>
       <c r="W7">
-        <v>0.1931067044381492</v>
+        <v>-0.1178977272727273</v>
       </c>
       <c r="X7">
-        <v>0.3774555190346738</v>
+        <v>0.2281377318265359</v>
       </c>
       <c r="Y7">
-        <v>-0.1843488145965246</v>
+        <v>-0.3460354590992631</v>
       </c>
       <c r="Z7">
-        <v>1.093023255813954</v>
+        <v>0.1767578125</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.2181424004712712</v>
+        <v>0.157266935669678</v>
       </c>
       <c r="AC7">
-        <v>-0.2181424004712712</v>
+        <v>-0.157266935669678</v>
       </c>
       <c r="AD7">
-        <v>178.2</v>
+        <v>98.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>178.2</v>
+        <v>98.5</v>
       </c>
       <c r="AG7">
-        <v>-38.40000000000001</v>
+        <v>-119</v>
       </c>
       <c r="AH7">
-        <v>0.7136563876651982</v>
+        <v>0.6668923493568044</v>
       </c>
       <c r="AI7">
-        <v>0.5586206896551724</v>
+        <v>0.436613475177305</v>
       </c>
       <c r="AJ7">
-        <v>-1.16012084592145</v>
+        <v>1.70487106017192</v>
       </c>
       <c r="AK7">
-        <v>-0.3750000000000001</v>
+        <v>-14.69135802469137</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1310,104 +1292,83 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.298</v>
-      </c>
-      <c r="E8">
-        <v>0.448</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>20.5</v>
-      </c>
-      <c r="L8">
-        <v>0.2871148459383753</v>
+        <v>-68.2</v>
       </c>
       <c r="M8">
-        <v>6.75</v>
+        <v>0.012</v>
       </c>
       <c r="N8">
-        <v>0.1618705035971223</v>
+        <v>0.0004761904761904762</v>
       </c>
       <c r="O8">
-        <v>0.3292682926829268</v>
+        <v>-0.0001759530791788856</v>
       </c>
       <c r="P8">
-        <v>6.75</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.1618705035971223</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3292682926829268</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>127.9</v>
+        <v>190.3</v>
       </c>
       <c r="V8">
-        <v>3.067146282973621</v>
+        <v>7.551587301587302</v>
       </c>
       <c r="W8">
-        <v>0.09932170542635659</v>
+        <v>-0.5070631970260223</v>
       </c>
       <c r="X8">
-        <v>0.7457067361183396</v>
+        <v>0.3649832930871937</v>
       </c>
       <c r="Y8">
-        <v>-0.6463850306919831</v>
+        <v>-0.8720464901132161</v>
       </c>
       <c r="Z8">
-        <v>0.2389558232931727</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.2315159176591471</v>
+        <v>0.1615977345201582</v>
       </c>
       <c r="AC8">
-        <v>-0.2315159176591471</v>
+        <v>-0.1615977345201582</v>
       </c>
       <c r="AD8">
-        <v>277.4</v>
+        <v>111.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>277.4</v>
+        <v>111.2</v>
       </c>
       <c r="AG8">
-        <v>149.5</v>
+        <v>-79.10000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.8693199623942338</v>
+        <v>0.81524926686217</v>
       </c>
       <c r="AI8">
-        <v>0.6734644331148337</v>
+        <v>0.6446376811594203</v>
       </c>
       <c r="AJ8">
-        <v>0.7819037656903765</v>
+        <v>1.467532467532467</v>
       </c>
       <c r="AK8">
-        <v>0.5264084507042253</v>
+        <v>4.443820224719099</v>
       </c>
       <c r="AL8">
         <v>0</v>
